--- a/resources/analysis_schema_quant_data_analysis_mortality_deaths_template.xlsx
+++ b/resources/analysis_schema_quant_data_analysis_mortality_deaths_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C49429-5272-4DFF-BA21-5F81AE9C268E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AAAF601-105B-4D80-B8FA-454017386E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="33">
   <si>
     <t>indicator_name</t>
   </si>
@@ -83,6 +83,42 @@
   </si>
   <si>
     <t>Location Healthcare Sought</t>
+  </si>
+  <si>
+    <t>Sex of deceased, by Strata</t>
+  </si>
+  <si>
+    <t>Cause of Death, by Strata</t>
+  </si>
+  <si>
+    <t>Location of Death, by Strata</t>
+  </si>
+  <si>
+    <t>Sought Healthcare, by Strata</t>
+  </si>
+  <si>
+    <t>Reason Not Sought Healthcare, by Strata</t>
+  </si>
+  <si>
+    <t>Location Healthcare Sought, by Strata</t>
+  </si>
+  <si>
+    <t>stratum</t>
+  </si>
+  <si>
+    <t>Cause of Death, by Sex</t>
+  </si>
+  <si>
+    <t>Location of Death, by Sex</t>
+  </si>
+  <si>
+    <t>Sought Healthcare, by Sex</t>
+  </si>
+  <si>
+    <t>Reason Not Sought Healthcare, by Sex</t>
+  </si>
+  <si>
+    <t>Location Healthcare Sought, by Sex</t>
   </si>
 </sst>
 </file>
@@ -943,10 +979,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" customWidth="1"/>
+    <col min="1" max="1" width="37.140625" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -1080,6 +1116,226 @@
         <v>10</v>
       </c>
     </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10">
+        <v>100</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12">
+        <v>100</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13">
+        <v>100</v>
+      </c>
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14">
+        <v>100</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15">
+        <v>100</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16">
+        <v>100</v>
+      </c>
+      <c r="G16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="G17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
